--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.66558949978201</v>
+        <v>6.445658293714577</v>
       </c>
       <c r="D2" t="n">
-        <v>38.5064052699564</v>
+        <v>6.257290856367915</v>
       </c>
       <c r="E2" t="n">
-        <v>10.77908869748421</v>
+        <v>1.751601913341184</v>
       </c>
       <c r="F2" t="n">
-        <v>13.34352799498946</v>
+        <v>2.168323299185789</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.60000033366267</v>
+        <v>4.160000054220183</v>
       </c>
       <c r="D3" t="n">
-        <v>26.9967399379374</v>
+        <v>4.386970239914826</v>
       </c>
       <c r="E3" t="n">
-        <v>10.77908869748421</v>
+        <v>1.751601913341184</v>
       </c>
       <c r="F3" t="n">
-        <v>13.34352799498946</v>
+        <v>2.168323299185789</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.59264290092148</v>
+        <v>3.996304471399741</v>
       </c>
       <c r="D4" t="n">
-        <v>24.49312757764576</v>
+        <v>3.980133231367436</v>
       </c>
       <c r="E4" t="n">
-        <v>10.77908869748421</v>
+        <v>1.751601913341184</v>
       </c>
       <c r="F4" t="n">
-        <v>13.34352799498946</v>
+        <v>2.168323299185789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.18365779249719</v>
+        <v>6.529844391280793</v>
       </c>
       <c r="D5" t="n">
-        <v>36.89772767108016</v>
+        <v>5.995880746550527</v>
       </c>
       <c r="E5" t="n">
-        <v>10.77908869748421</v>
+        <v>1.751601913341184</v>
       </c>
       <c r="F5" t="n">
-        <v>13.34352799498946</v>
+        <v>2.168323299185789</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.24093964956667</v>
+        <v>2.801652693054583</v>
       </c>
       <c r="D6" t="n">
-        <v>6.665529995691023</v>
+        <v>1.083148624299791</v>
       </c>
       <c r="E6" t="n">
-        <v>10.77908869748421</v>
+        <v>1.751601913341184</v>
       </c>
       <c r="F6" t="n">
-        <v>13.34352799498946</v>
+        <v>2.168323299185789</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.57241150239744</v>
+        <v>2.530516869139583</v>
       </c>
       <c r="D7" t="n">
-        <v>12.41314230149858</v>
+        <v>2.017135623993519</v>
       </c>
       <c r="E7" t="n">
-        <v>10.77908869748421</v>
+        <v>1.751601913341184</v>
       </c>
       <c r="F7" t="n">
-        <v>13.34352799498946</v>
+        <v>2.168323299185789</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.07096549884061</v>
+        <v>7.1615318935616</v>
       </c>
       <c r="D8" t="n">
-        <v>46.62873320739347</v>
+        <v>7.57716914620144</v>
       </c>
       <c r="E8" t="n">
-        <v>10.77908869748421</v>
+        <v>1.751601913341184</v>
       </c>
       <c r="F8" t="n">
-        <v>13.34352799498946</v>
+        <v>2.168323299185789</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
